--- a/05machine_learning/5차원데이터/4차원데이터 - 복사본 (2)/3차원데이터 - 복사본 (2).xlsx
+++ b/05machine_learning/5차원데이터/4차원데이터 - 복사본 (2)/3차원데이터 - 복사본 (2).xlsx
@@ -5,11 +5,11 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haram\OneDrive\문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fintech\05machine_learning\5차원데이터\4차원데이터 - 복사본 (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11340" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11340" tabRatio="500" activeTab="2"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="2차원" sheetId="1" r:id="rId4"/>
@@ -21,15 +21,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="5">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+  <x:si>
+    <x:t>(1,5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(5, 1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>열벡터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행벡터</x:t>
+  </x:si>
   <x:si>
     <x:t>1열</x:t>
   </x:si>
   <x:si>
-    <x:t>2열</x:t>
+    <x:t>3열</x:t>
   </x:si>
   <x:si>
-    <x:t>3열</x:t>
+    <x:t>2열</x:t>
   </x:si>
   <x:si>
     <x:t>4열</x:t>
@@ -74,7 +86,7 @@
       <x:color rgb="ff000000"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -90,6 +102,12 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd9d9d9"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="fff2f2f2"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -110,13 +128,16 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <x:cellXfs count="5">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -145,8 +166,34 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:cellXfs>
-  <x:cellStyles count="1">
+  <x:cellStyles count="2">
     <x:cellStyle name="표준" xfId="0" builtinId="0" iLevel="0"/>
   </x:cellStyles>
   <x:dxfs count="12">
@@ -865,7 +912,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:E6"/>
+  <x:dimension ref="A1:G16"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="5" width="9.00390625" bestFit="1" customWidth="1"/>
@@ -873,19 +920,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -973,8 +1020,66 @@
         <x:v>9</x:v>
       </x:c>
     </x:row>
+    <x:row r="9" spans="1:7">
+      <x:c r="A9" s="2">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B9" s="2">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C9" s="2">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D9" s="2">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E9" s="2">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:1">
+      <x:c r="A10" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:1">
+      <x:c r="A11" s="3">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:1">
+      <x:c r="A12" s="3">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:1">
+      <x:c r="A13" s="3">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:1">
+      <x:c r="A14" s="3">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:1">
+      <x:c r="A15" s="3">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:1">
+      <x:c r="A16" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -990,19 +1095,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1091,7 +1196,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
@@ -1107,19 +1212,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1208,7 +1313,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51180553436279296875" footer="0.51180553436279296875"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51166665554046630859" footer="0.51166665554046630859"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>